--- a/output/2026-09-05_09_Italia_Calabria_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-05_09_Italia_Calabria_Utensilerie_e_Macchine_Utensili.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Attiva dal 1990, rivenditrice di macchine/utensili per legno, impianti di aspirazione/verniciatura/aria compressa - buon target per distribuzione sistemi aspirazione.</t>
+          <t>Attiva dal 1990, rivenditrice di macchine/utensili per legno, impianti di aspirazione/verniciatura/aria compressa - buon target per distribuzione sistemi aspirazione. [DUPLICATO — vedi anche: 2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>P.IVA 02764430803, sito ufficiale confermato.</t>
+          <t>P.IVA 02764430803, sito ufficiale confermato. [DUPLICATO — vedi anche: 2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -657,7 +657,6 @@
           <t>CV Anser F.lli Zicarelli S.r.l.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Cosenza (CS) - sede a Paola</t>
@@ -690,7 +689,6 @@
           <t>Vero S.a.s. di Rosario Scidone &amp; C.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Reggio Calabria (RC) - sede a Palmi</t>
